--- a/요양병원_목록.xlsx
+++ b/요양병원_목록.xlsx
@@ -1902,7 +1902,11 @@
           <t>031-760-3691</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>srcrecruit@naver.com</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
@@ -2010,7 +2014,11 @@
           <t>031-528-8899</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>toojeam8899@naver.com</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
@@ -3042,7 +3050,11 @@
           <t>032-612-0056</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>biglove0056@naver.com</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
@@ -3086,7 +3098,11 @@
           <t>1877-5661</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>km.kim1@lottebobath.net</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
@@ -4174,7 +4190,11 @@
           <t>031-406-7777</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>sas9955@naver.com</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
@@ -8102,7 +8122,11 @@
           <t>055-755-7000</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>mokhwa8000@naver.com</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
@@ -14010,7 +14034,11 @@
           <t>042-272-9633</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>cmisilver@nate.com</t>
+        </is>
+      </c>
       <c r="E645" t="inlineStr"/>
       <c r="F645" t="inlineStr">
         <is>
@@ -14362,7 +14390,11 @@
           <t>042-528-0001</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>yangnyeong09@naver.com</t>
+        </is>
+      </c>
       <c r="E661" t="inlineStr"/>
       <c r="F661" t="inlineStr">
         <is>
@@ -14686,7 +14718,11 @@
           <t>042-256-1177</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>wellciti@wellciti.com</t>
+        </is>
+      </c>
       <c r="E676" t="inlineStr"/>
       <c r="F676" t="inlineStr">
         <is>
@@ -15098,7 +15134,11 @@
           <t>051-516-9898</t>
         </is>
       </c>
-      <c r="D695" t="inlineStr"/>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>kovid21@naver.com</t>
+        </is>
+      </c>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="inlineStr">
         <is>
@@ -15142,7 +15182,11 @@
           <t>051-714-0098</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>sgpark736@hanmail.net</t>
+        </is>
+      </c>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="inlineStr">
         <is>
@@ -16290,7 +16334,11 @@
           <t>051-328-8251</t>
         </is>
       </c>
-      <c r="D752" t="inlineStr"/>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>3288251@naver.com</t>
+        </is>
+      </c>
       <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr">
         <is>
@@ -17494,7 +17542,11 @@
           <t>051-582-7001</t>
         </is>
       </c>
-      <c r="D809" t="inlineStr"/>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>tema4949@naver.com</t>
+        </is>
+      </c>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="inlineStr">
         <is>
@@ -19074,7 +19126,11 @@
           <t>02-848-0100</t>
         </is>
       </c>
-      <c r="D884" t="inlineStr"/>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>hmp0100@noksib.com</t>
+        </is>
+      </c>
       <c r="E884" t="inlineStr"/>
       <c r="F884" t="inlineStr">
         <is>
@@ -19298,7 +19354,11 @@
           <t>521-8275</t>
         </is>
       </c>
-      <c r="D895" t="inlineStr"/>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>seocho8275@naver.com</t>
+        </is>
+      </c>
       <c r="E895" t="inlineStr"/>
       <c r="F895" t="inlineStr">
         <is>
@@ -20158,7 +20218,11 @@
           <t>044-865-0066</t>
         </is>
       </c>
-      <c r="D935" t="inlineStr"/>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>suneun0066@daum.net</t>
+        </is>
+      </c>
       <c r="E935" t="inlineStr"/>
       <c r="F935" t="inlineStr">
         <is>
@@ -20730,7 +20794,11 @@
           <t>052-239-0669</t>
         </is>
       </c>
-      <c r="D962" t="inlineStr"/>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>jmhos@hanmail.net</t>
+        </is>
+      </c>
       <c r="E962" t="inlineStr"/>
       <c r="F962" t="inlineStr">
         <is>
@@ -21166,7 +21234,11 @@
           <t>032-710-6001</t>
         </is>
       </c>
-      <c r="D983" t="inlineStr"/>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>naeun6201@naver.com</t>
+        </is>
+      </c>
       <c r="E983" t="inlineStr"/>
       <c r="F983" t="inlineStr">
         <is>
@@ -24894,7 +24966,11 @@
           <t>063-220-9302</t>
         </is>
       </c>
-      <c r="D1163" t="inlineStr"/>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>wc01@yeonsue.com</t>
+        </is>
+      </c>
       <c r="E1163" t="inlineStr"/>
       <c r="F1163" t="inlineStr">
         <is>
@@ -25126,7 +25202,11 @@
           <t>063-228-1122</t>
         </is>
       </c>
-      <c r="D1174" t="inlineStr"/>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>hanos1@hanmail.net</t>
+        </is>
+      </c>
       <c r="E1174" t="inlineStr"/>
       <c r="F1174" t="inlineStr">
         <is>
@@ -26066,7 +26146,11 @@
           <t>041-834-5114</t>
         </is>
       </c>
-      <c r="D1218" t="inlineStr"/>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>hanchul59@hanmail.net</t>
+        </is>
+      </c>
       <c r="E1218" t="inlineStr"/>
       <c r="F1218" t="inlineStr">
         <is>
@@ -26562,7 +26646,11 @@
           <t>041-565-2300</t>
         </is>
       </c>
-      <c r="D1242" t="inlineStr"/>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>cwj0513@naver.com</t>
+        </is>
+      </c>
       <c r="E1242" t="inlineStr"/>
       <c r="F1242" t="inlineStr">
         <is>
